--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1075B857-8441-44D5-94DB-85B70AB41555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281B1B88-E3C4-4051-8F6B-F32C476D8BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -1282,392 +1282,212 @@
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="7">
-        <v>1688750</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="7">
-        <v>868401</v>
-      </c>
+      <c r="A39" s="6"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="6">
-        <v>45903</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="7">
-        <v>1089458</v>
-      </c>
+      <c r="A40" s="6"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="6">
-        <v>45904</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="7">
-        <v>674363</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="6">
-        <v>45905</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="7">
-        <v>2271533</v>
-      </c>
+      <c r="A42" s="6"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="6">
-        <v>45906</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1433831</v>
-      </c>
+      <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="6">
-        <v>45907</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="7">
-        <v>1522757</v>
-      </c>
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="6">
-        <v>45908</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="7">
-        <v>917334</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="6">
-        <v>45909</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="7">
-        <v>892615</v>
-      </c>
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6">
-        <v>45910</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" s="7">
-        <v>3059875</v>
-      </c>
+      <c r="A47" s="6"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6">
-        <v>45911</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="7">
-        <v>793193</v>
-      </c>
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6">
-        <v>45912</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="7">
-        <v>963219</v>
-      </c>
+      <c r="A49" s="6"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6">
-        <v>45913</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" s="7">
-        <v>1160612</v>
-      </c>
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6">
-        <v>45914</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="7">
-        <v>1162274</v>
-      </c>
+      <c r="A51" s="6"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6">
-        <v>45915</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="7">
-        <v>2022150</v>
-      </c>
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="6">
-        <v>45916</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="7">
-        <v>967098</v>
-      </c>
+      <c r="A53" s="6"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="6">
-        <v>45917</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54" s="7">
-        <v>909920</v>
-      </c>
+      <c r="A54" s="6"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="6">
-        <v>45918</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="7">
-        <v>850233</v>
-      </c>
+      <c r="A55" s="6"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="6">
-        <v>45919</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="7">
-        <v>639466</v>
-      </c>
+      <c r="A56" s="6"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="6">
-        <v>45920</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57" s="7">
-        <v>3748695</v>
-      </c>
+      <c r="A57" s="6"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="6">
-        <v>45921</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="7">
-        <v>1566704</v>
-      </c>
+      <c r="A58" s="6"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="6">
-        <v>45922</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C59" s="7">
-        <v>853594</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="6">
-        <v>45923</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="7">
-        <v>1390475</v>
-      </c>
+      <c r="A60" s="6"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="6">
-        <v>45924</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" s="7">
-        <v>866091</v>
-      </c>
+      <c r="A61" s="6"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="6">
-        <v>45925</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C62" s="7">
-        <v>1329749</v>
-      </c>
+      <c r="A62" s="6"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A63" s="6">
-        <v>45926</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C63" s="7">
-        <v>847455</v>
-      </c>
+      <c r="A63" s="6"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A64" s="6">
-        <v>45927</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64" s="7">
-        <v>1062739</v>
-      </c>
+      <c r="A64" s="6"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="6">
-        <v>45928</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="7">
-        <v>1375850</v>
-      </c>
+      <c r="A65" s="6"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A66" s="6">
-        <v>45929</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" s="7">
-        <v>874245</v>
-      </c>
+      <c r="A66" s="6"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A67" s="6">
-        <v>45930</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C67" s="7">
-        <v>1448251</v>
-      </c>
+      <c r="A67" s="6"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1719</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1720</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -210,17 +210,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,14 +272,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,16 +285,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -277,8 +299,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,46 +317,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,7 +332,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -368,7 +368,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +434,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,103 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,71 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -660,11 +595,76 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,127 +695,127 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1720"/>
+  <dimension ref="A1:E1721"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22980,8 +22980,19 @@
         <v>271281</v>
       </c>
     </row>
+    <row r="1721" spans="1:3">
+      <c r="A1721" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1721">
+        <v>409607</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1719">
+  <autoFilter ref="A1:E1720">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1720</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,15 +203,63 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,30 +275,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,28 +283,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,8 +302,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -315,35 +333,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +386,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,43 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,25 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,61 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,16 +572,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -589,8 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,26 +610,37 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -651,20 +662,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -821,14 +821,14 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1721"/>
+  <dimension ref="A1:E1722"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22991,8 +22991,19 @@
         <v>409607</v>
       </c>
     </row>
+    <row r="1722" spans="1:3">
+      <c r="A1722" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1722">
+        <v>613278</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1720">
+  <autoFilter ref="A1:E1721">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,7 +205,51 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,14 +264,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,25 +278,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,29 +324,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -314,29 +337,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,6 +362,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,7 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +416,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,31 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,19 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,19 +500,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,11 +628,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,202 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1722"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23002,8 +23002,19 @@
         <v>613278</v>
       </c>
     </row>
+    <row r="1723" spans="1:3">
+      <c r="A1723" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1723">
+        <v>2796086</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1721">
+  <autoFilter ref="A1:E1722">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,11 +203,85 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,10 +299,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -240,16 +315,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,13 +331,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -278,70 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,49 +470,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,25 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,24 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -613,16 +595,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -645,26 +627,44 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23013,8 +23013,19 @@
         <v>2796086</v>
       </c>
     </row>
+    <row r="1724" spans="1:3">
+      <c r="A1724" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1724">
+        <v>736036</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1722">
+  <autoFilter ref="A1:E1723">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,21 +249,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,15 +263,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,37 +287,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -307,9 +309,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -323,27 +332,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +386,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +452,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,133 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,41 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,20 +595,28 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +638,33 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1724"/>
+  <dimension ref="A1:E1725"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23024,8 +23024,19 @@
         <v>736036</v>
       </c>
     </row>
+    <row r="1725" spans="1:3">
+      <c r="A1725" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1725">
+        <v>407704</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1723">
+  <autoFilter ref="A1:E1724">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,65 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -285,9 +226,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,29 +294,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -333,7 +303,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,163 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,30 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,6 +597,48 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -632,24 +650,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1725"/>
+  <dimension ref="A1:E1726"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23035,8 +23035,19 @@
         <v>407704</v>
       </c>
     </row>
+    <row r="1726" spans="1:3">
+      <c r="A1726" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1726">
+        <v>555379</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1724">
+  <autoFilter ref="A1:E1725">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -211,16 +226,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,63 +249,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,13 +279,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -324,8 +286,15 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -346,6 +315,37 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,13 +362,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,25 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,25 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,73 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -525,24 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,26 +606,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,32 +628,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +648,187 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1726"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23046,8 +23046,19 @@
         <v>555379</v>
       </c>
     </row>
+    <row r="1727" spans="1:3">
+      <c r="A1727" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1727">
+        <v>335090</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1725">
+  <autoFilter ref="A1:E1726">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,16 +210,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,21 +227,54 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,9 +288,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,6 +298,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,26 +325,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -323,25 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,43 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,13 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +446,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,65 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,65 +649,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1728"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23057,8 +23057,19 @@
         <v>335090</v>
       </c>
     </row>
+    <row r="1728" spans="1:3">
+      <c r="A1728" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1728">
+        <v>1713538</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1726">
+  <autoFilter ref="A1:E1727">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,38 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,38 +247,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -256,11 +254,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -280,9 +285,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,50 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,13 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,49 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,19 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,39 +636,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -652,19 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1728"/>
+  <dimension ref="A1:E1729"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23068,8 +23068,19 @@
         <v>1713538</v>
       </c>
     </row>
+    <row r="1729" spans="1:3">
+      <c r="A1729" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1729">
+        <v>488909</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1727">
+  <autoFilter ref="A1:E1728">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -203,23 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,31 +226,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -269,30 +242,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -308,11 +265,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -324,9 +294,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +333,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,6 +368,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -386,19 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +404,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,13 +428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,19 +452,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,43 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -589,8 +604,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,6 +630,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,44 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1729"/>
+  <dimension ref="A1:E1730"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23079,8 +23079,19 @@
         <v>488909</v>
       </c>
     </row>
+    <row r="1730" spans="1:3">
+      <c r="A1730" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1730">
+        <v>598810</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1728">
+  <autoFilter ref="A1:E1729">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,122 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,97 +334,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,30 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +470,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,133 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,32 +571,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,15 +600,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,16 +629,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1730"/>
+  <dimension ref="A1:E1731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23090,8 +23090,19 @@
         <v>598810</v>
       </c>
     </row>
+    <row r="1731" spans="1:3">
+      <c r="A1731" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1731">
+        <v>383449</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1729">
+  <autoFilter ref="A1:E1730">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -211,6 +211,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -219,15 +242,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,7 +265,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,24 +280,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,11 +294,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,8 +308,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,32 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,31 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +452,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +470,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,37 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,15 +600,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,17 +628,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,13 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,140 +695,140 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1731"/>
+  <dimension ref="A1:E1732"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23101,8 +23101,19 @@
         <v>383449</v>
       </c>
     </row>
+    <row r="1732" spans="1:3">
+      <c r="A1732" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1732">
+        <v>342342</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1730">
+  <autoFilter ref="A1:E1731">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,7 +205,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,15 +213,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,15 +234,52 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,28 +293,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -294,6 +301,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -301,23 +309,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -334,7 +327,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +335,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,97 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,15 +597,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,11 +627,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +658,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1732"/>
+  <dimension ref="A1:E1733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23112,8 +23112,16 @@
         <v>342342</v>
       </c>
     </row>
+    <row r="1733" spans="1:2">
+      <c r="A1733" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1731">
+  <autoFilter ref="A1:E1732">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1810">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,46 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,9 +221,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,22 +250,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -302,8 +257,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,7 +274,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,16 +325,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,79 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,19 +428,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,19 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +488,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -597,6 +615,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,48 +660,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1734"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23134,8 +23134,19 @@
         <v>363707</v>
       </c>
     </row>
+    <row r="1735" spans="1:3">
+      <c r="A1735" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1735">
+        <v>352896</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1733">
+  <autoFilter ref="A1:E1734">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1735</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,8 +204,45 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,19 +256,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -251,59 +279,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -319,15 +303,31 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +416,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,79 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,31 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,19 +512,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,35 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -622,23 +604,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +659,176 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1735"/>
+  <dimension ref="A1:E1736"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23145,8 +23145,19 @@
         <v>352896</v>
       </c>
     </row>
+    <row r="1736" spans="1:3">
+      <c r="A1736" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1736">
+        <v>237378</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1734">
+  <autoFilter ref="A1:E1735">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1735</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,30 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -212,7 +235,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,51 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,15 +296,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,24 +325,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,85 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,25 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,21 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -604,7 +589,18 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -613,8 +609,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,6 +630,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -648,45 +668,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,140 +695,140 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1736"/>
+  <dimension ref="A1:E1737"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23156,8 +23156,19 @@
         <v>237378</v>
       </c>
     </row>
+    <row r="1737" spans="1:3">
+      <c r="A1737" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1737">
+        <v>186385</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1735">
+  <autoFilter ref="A1:E1736">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -167,8 +167,8 @@
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,37 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -243,6 +212,36 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,23 +263,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,7 +303,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,30 +318,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,7 +327,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +428,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,43 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,19 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,19 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -589,8 +604,41 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,15 +649,6 @@
         <color theme="4"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -629,61 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,140 +695,140 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1737"/>
+  <dimension ref="A1:E1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23167,8 +23167,19 @@
         <v>186385</v>
       </c>
     </row>
+    <row r="1738" spans="1:3">
+      <c r="A1738" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1738">
+        <v>790430</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1736">
+  <autoFilter ref="A1:E1737">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,53 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,8 +226,106 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -286,64 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,24 +428,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -410,13 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,49 +452,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,6 +506,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,24 +597,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +636,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1738"/>
+  <dimension ref="A1:E1739"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23178,8 +23178,19 @@
         <v>790430</v>
       </c>
     </row>
+    <row r="1739" spans="1:3">
+      <c r="A1739" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1739">
+        <v>214575</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1737">
+  <autoFilter ref="A1:E1738">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,6 +233,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -227,13 +257,34 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -249,45 +300,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,29 +311,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,6 +325,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -340,10 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +374,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +416,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,61 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,55 +595,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +618,217 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1739"/>
+  <dimension ref="A1:E1740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23189,8 +23189,19 @@
         <v>214575</v>
       </c>
     </row>
+    <row r="1740" spans="1:3">
+      <c r="A1740" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1740">
+        <v>205229</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1738">
+  <autoFilter ref="A1:E1739">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,21 +210,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -233,39 +218,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,18 +239,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,7 +257,39 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,14 +303,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -339,9 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +434,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,55 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,13 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,37 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,6 +603,32 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -604,37 +636,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,118 +674,118 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -794,41 +794,41 @@
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1740"/>
+  <dimension ref="A1:E1741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23200,8 +23200,19 @@
         <v>205229</v>
       </c>
     </row>
+    <row r="1741" spans="1:3">
+      <c r="A1741" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1741">
+        <v>193912</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1739">
+  <autoFilter ref="A1:E1740">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,10 +203,34 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -219,9 +243,39 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -234,6 +288,29 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,86 +334,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,36 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -404,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +386,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +404,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,18 +470,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -506,13 +482,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,19 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,26 +603,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,17 +628,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,9 +651,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1741"/>
+  <dimension ref="A1:E1742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23211,8 +23211,19 @@
         <v>193912</v>
       </c>
     </row>
+    <row r="1742" spans="1:3">
+      <c r="A1742" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1742">
+        <v>243553</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1740">
+  <autoFilter ref="A1:E1741">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -203,9 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,37 +212,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,38 +240,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,7 +273,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,7 +303,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,21 +342,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +410,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,31 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,43 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,61 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,8 +613,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,176 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1742"/>
+  <dimension ref="A1:E1743"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23222,8 +23222,19 @@
         <v>243553</v>
       </c>
     </row>
+    <row r="1743" spans="1:3">
+      <c r="A1743" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1743">
+        <v>2427566</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1741">
+  <autoFilter ref="A1:E1742">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,29 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -234,7 +211,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,22 +226,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,7 +241,53 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,28 +301,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -317,18 +309,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +374,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +422,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,145 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -595,26 +586,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,17 +610,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,6 +642,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1743"/>
+  <dimension ref="A1:E1744"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23233,8 +23233,19 @@
         <v>2427566</v>
       </c>
     </row>
+    <row r="1744" spans="1:3">
+      <c r="A1744" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1744">
+        <v>278318</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1742">
+  <autoFilter ref="A1:E1743">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -204,6 +204,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -211,21 +218,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,9 +232,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,10 +279,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -270,9 +295,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,19 +309,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -309,26 +324,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,19 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,43 +428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,19 +458,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,85 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,41 +586,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,11 +619,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1744"/>
+  <dimension ref="A1:E1745"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23244,8 +23244,19 @@
         <v>278318</v>
       </c>
     </row>
+    <row r="1745" spans="1:3">
+      <c r="A1745" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1745">
+        <v>301421</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1743">
+  <autoFilter ref="A1:E1744">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,13 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -218,22 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,15 +219,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,54 +233,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,8 +264,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,9 +281,69 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,55 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +446,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +470,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,19 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,19 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,32 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -590,21 +616,21 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -614,7 +640,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -642,193 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1745"/>
+  <dimension ref="A1:E1746"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23255,8 +23255,19 @@
         <v>301421</v>
       </c>
     </row>
+    <row r="1746" spans="1:3">
+      <c r="A1746" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1746">
+        <v>301421</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1744">
+  <autoFilter ref="A1:E1745">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,9 +217,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,46 +226,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,18 +247,58 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -318,32 +318,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,73 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,79 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,69 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,69 +660,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -674,25 +674,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -701,134 +701,134 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1747"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23266,8 +23266,19 @@
         <v>301421</v>
       </c>
     </row>
+    <row r="1747" spans="1:3">
+      <c r="A1747" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1747">
+        <v>294245</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1745">
+  <autoFilter ref="A1:E1746">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,62 +217,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,7 +242,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,16 +286,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,16 +333,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,43 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,19 +452,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,28 +624,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1747"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23277,8 +23277,19 @@
         <v>294245</v>
       </c>
     </row>
+    <row r="1748" spans="1:3">
+      <c r="A1748" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1748">
+        <v>216390</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1746">
+  <autoFilter ref="A1:E1747">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,8 +210,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,13 +242,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,23 +256,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,14 +273,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -286,16 +286,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,16 +316,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +446,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,151 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,20 +573,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,17 +610,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,9 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -821,14 +821,14 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1748"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23288,8 +23288,19 @@
         <v>216390</v>
       </c>
     </row>
+    <row r="1749" spans="1:3">
+      <c r="A1749" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1749">
+        <v>801201</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1747">
+  <autoFilter ref="A1:E1748">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,15 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -226,46 +227,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,8 +263,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,6 +302,36 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -317,31 +340,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,67 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +476,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,61 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,6 +573,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -595,21 +606,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -624,6 +620,21 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,165 +668,154 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23299,8 +23299,19 @@
         <v>801201</v>
       </c>
     </row>
+    <row r="1750" spans="1:3">
+      <c r="A1750" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1750">
+        <v>240216</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1748">
+  <autoFilter ref="A1:E1749">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,8 +166,8 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,46 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,15 +234,76 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,14 +318,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,48 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,67 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,97 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,17 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,15 +604,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -635,6 +615,41 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,37 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1750"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23310,8 +23310,30 @@
         <v>240216</v>
       </c>
     </row>
+    <row r="1751" spans="1:3">
+      <c r="A1751" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1751">
+        <v>240216</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:3">
+      <c r="A1752" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1752">
+        <v>350979</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1749">
+  <autoFilter ref="A1:E1751">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1752</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,22 +204,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,26 +248,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,33 +271,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -309,23 +286,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,11 +310,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +398,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +452,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,25 +506,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,8 +573,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -599,7 +601,31 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,17 +641,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,23 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1752"/>
+  <dimension ref="A1:E1753"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23332,8 +23332,19 @@
         <v>350979</v>
       </c>
     </row>
+    <row r="1753" spans="1:3">
+      <c r="A1753" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1753">
+        <v>296040</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1751">
+  <autoFilter ref="A1:E1752">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1752</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,24 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,40 +235,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -264,47 +250,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,14 +264,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -340,8 +308,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,49 +416,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +440,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +470,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,31 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,6 +582,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -600,8 +609,38 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,45 +663,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1753"/>
+  <dimension ref="A1:E1754"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23343,8 +23343,19 @@
         <v>296040</v>
       </c>
     </row>
+    <row r="1754" spans="1:3">
+      <c r="A1754" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1754">
+        <v>242997</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1752">
+  <autoFilter ref="A1:E1753">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,114 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,6 +227,97 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -341,7 +326,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +380,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,37 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,13 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +482,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,43 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,26 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -608,6 +588,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -615,17 +606,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1754"/>
+  <dimension ref="A1:E1755"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23354,8 +23354,19 @@
         <v>242997</v>
       </c>
     </row>
+    <row r="1755" spans="1:3">
+      <c r="A1755" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1755">
+        <v>3146972</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1753">
+  <autoFilter ref="A1:E1754">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,30 +204,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,7 +234,61 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,45 +309,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -310,23 +317,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,163 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -593,15 +608,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,23 +624,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,16 +646,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1755"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23365,8 +23365,19 @@
         <v>3146972</v>
       </c>
     </row>
+    <row r="1756" spans="1:3">
+      <c r="A1756" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1756">
+        <v>283989</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1754">
+  <autoFilter ref="A1:E1755">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,82 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -219,14 +295,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,53 +303,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,15 +318,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,37 +333,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,49 +422,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +470,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,46 +586,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +628,43 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1757"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23376,8 +23376,16 @@
         <v>283989</v>
       </c>
     </row>
+    <row r="1757" spans="1:2">
+      <c r="A1757" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1755">
+  <autoFilter ref="A1:E1756">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,51 +254,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -277,24 +262,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,7 +280,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,9 +294,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +318,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +440,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,121 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +495,54 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -595,35 +619,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,16 +654,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1758"/>
+  <dimension ref="A1:E1760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23398,8 +23398,30 @@
         <v>284823</v>
       </c>
     </row>
+    <row r="1759" spans="1:3">
+      <c r="A1759" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1759">
+        <v>284823</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:3">
+      <c r="A1760" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1760">
+        <v>339378</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1757">
+  <autoFilter ref="A1:E1759">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1760</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,52 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,9 +219,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,22 +235,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -309,8 +251,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,6 +282,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -339,9 +319,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,49 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,43 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,21 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,26 +604,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +644,191 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1760"/>
+  <dimension ref="A1:E1761"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23420,8 +23420,19 @@
         <v>339378</v>
       </c>
     </row>
+    <row r="1761" spans="1:3">
+      <c r="A1761" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1761">
+        <v>884717</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759">
+  <autoFilter ref="A1:E1760">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1760</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,72 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -213,6 +279,29 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -228,92 +317,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,13 +331,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -340,10 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,25 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,48 +410,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -470,7 +422,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -589,17 +583,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,11 +606,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,9 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1761"/>
+  <dimension ref="A1:E1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23431,8 +23431,19 @@
         <v>884717</v>
       </c>
     </row>
+    <row r="1762" spans="1:3">
+      <c r="A1762" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1762">
+        <v>371581</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1760">
+  <autoFilter ref="A1:E1761">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,30 +217,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,25 +255,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,31 +278,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -346,6 +307,45 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +404,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +458,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,43 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -590,40 +629,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,21 +654,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1762"/>
+  <dimension ref="A1:E1763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23442,8 +23442,19 @@
         <v>371581</v>
       </c>
     </row>
+    <row r="1763" spans="1:3">
+      <c r="A1763" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1763">
+        <v>295556</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1761">
+  <autoFilter ref="A1:E1762">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,13 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -218,7 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,15 +219,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,6 +241,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -262,9 +278,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,10 +293,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,7 +309,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,15 +331,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -333,15 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,67 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +434,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,37 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,48 +586,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -660,10 +618,52 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1763"/>
+  <dimension ref="A1:E1764"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23453,8 +23453,19 @@
         <v>295556</v>
       </c>
     </row>
+    <row r="1764" spans="1:3">
+      <c r="A1764" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1764">
+        <v>363613</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1762">
+  <autoFilter ref="A1:E1763">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,14 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -217,69 +225,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,7 +248,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,10 +263,58 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -331,17 +326,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,73 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,97 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -597,6 +623,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,30 +654,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -651,20 +662,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23464,8 +23464,19 @@
         <v>363613</v>
       </c>
     </row>
+    <row r="1765" spans="1:3">
+      <c r="A1765" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1765">
+        <v>286033</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1764">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">

--- a/dashboard/data/incoming/dショッピング.xlsx
+++ b/dashboard/data/incoming/dショッピング.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,16 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,9 +226,48 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -241,7 +280,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,22 +318,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -287,40 +325,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +440,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,67 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -597,17 +582,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,10 +601,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1765"/>
+  <dimension ref="A1:E1766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23475,8 +23475,19 @@
         <v>286033</v>
       </c>
     </row>
+    <row r="1766" spans="1:3">
+      <c r="A1766" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1766">
+        <v>934663</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1764">
+  <autoFilter ref="A1:E1765">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:E1809">
